--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6435-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6435-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11486560-D27E-41E1-8D41-90125B32C5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9750E266-B67D-4F17-A4EB-EC468CC1C61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{C26F7A65-A5C0-4DD1-9673-506494269C23}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2E1591F4-8F30-46BE-80BA-B68FF11B7B5E}"/>
   </bookViews>
   <sheets>
     <sheet name="6435-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1397,22 +1397,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA1D93F-11DE-4DD3-A6EB-7F73B1006A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F837B33C-A8B1-4AA0-A38E-FD8353484AEB}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="6" width="7.6640625" customWidth="1"/>
-    <col min="7" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1440,7 @@
       <c r="Q1" s="26"/>
       <c r="R1" s="18"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1470,7 +1470,7 @@
       <c r="Q2" s="28"/>
       <c r="R2" s="29"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1566,7 +1566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>2026</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>2025</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>2024</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>2023</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>2022</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>2021</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>2020</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>2019</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>2018</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>2017</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>2016</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="35">
         <v>2015</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>2014</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>25</v>
       </c>
